--- a/products/soccer-mom-command-center/Soccer_Mom_Command_Center.xlsx
+++ b/products/soccer-mom-command-center/Soccer_Mom_Command_Center.xlsx
@@ -534,7 +534,12 @@
           </val>
         </ser>
         <dLbls>
-          <showPercent val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>
@@ -701,7 +706,12 @@
           </val>
         </ser>
         <dLbls>
-          <showPercent val="1"/>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="0"/>
+          <showBubbleSize val="0"/>
         </dLbls>
         <firstSliceAng val="0"/>
         <holeSize val="10"/>
@@ -848,7 +858,7 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>13</row>
       <rowOff>0</rowOff>
@@ -2858,7 +2868,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>46180</v>
+        <v>46181</v>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
@@ -2888,7 +2898,7 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
@@ -2918,7 +2928,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
@@ -2948,7 +2958,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
@@ -2978,7 +2988,7 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
@@ -3008,7 +3018,7 @@
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
@@ -3038,7 +3048,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
@@ -3068,7 +3078,7 @@
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
@@ -3098,7 +3108,7 @@
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
@@ -3128,7 +3138,7 @@
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
@@ -5335,7 +5345,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>46187</v>
+        <v>46188</v>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
@@ -5394,7 +5404,7 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
-        <v>46194</v>
+        <v>46195</v>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
@@ -5453,7 +5463,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
@@ -5512,7 +5522,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
@@ -5571,7 +5581,7 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
@@ -5630,7 +5640,7 @@
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
@@ -5689,7 +5699,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
@@ -5748,7 +5758,7 @@
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B12" s="18" t="inlineStr">
         <is>
@@ -5807,7 +5817,7 @@
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
@@ -5866,7 +5876,7 @@
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B14" s="18" t="inlineStr">
         <is>
@@ -5925,7 +5935,7 @@
     </row>
     <row r="15">
       <c r="A15" s="13" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
@@ -5984,7 +5994,7 @@
     </row>
     <row r="16">
       <c r="A16" s="17" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="B16" s="18" t="inlineStr">
         <is>
@@ -6628,7 +6638,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>46191</v>
+        <v>46192</v>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
@@ -6663,7 +6673,7 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
-        <v>46193</v>
+        <v>46194</v>
       </c>
       <c r="B6" s="19" t="inlineStr">
         <is>
@@ -6698,7 +6708,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
@@ -6733,7 +6743,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
@@ -6768,7 +6778,7 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>46200</v>
+        <v>46201</v>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
@@ -6803,7 +6813,7 @@
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
@@ -6838,7 +6848,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
@@ -6873,7 +6883,7 @@
     </row>
     <row r="12">
       <c r="A12" s="17" t="n">
-        <v>46208</v>
+        <v>46209</v>
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
@@ -6908,7 +6918,7 @@
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
@@ -6943,7 +6953,7 @@
     </row>
     <row r="14">
       <c r="A14" s="17" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
@@ -7884,7 +7894,7 @@
         </is>
       </c>
       <c r="G5" s="13" t="n">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="H5" s="35" t="n">
         <v>89.98999999999999</v>
@@ -7925,7 +7935,7 @@
         </is>
       </c>
       <c r="G6" s="17" t="n">
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="H6" s="28" t="n">
         <v>49.99</v>
@@ -7962,7 +7972,7 @@
         </is>
       </c>
       <c r="G7" s="13" t="n">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="H7" s="35" t="n">
         <v>32</v>
@@ -7999,7 +8009,7 @@
         </is>
       </c>
       <c r="G8" s="17" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H8" s="28" t="n">
         <v>18</v>
@@ -8036,7 +8046,7 @@
         </is>
       </c>
       <c r="G9" s="13" t="n">
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="H9" s="35" t="n">
         <v>65</v>
@@ -8073,7 +8083,7 @@
         </is>
       </c>
       <c r="G10" s="17" t="n">
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="H10" s="28" t="n">
         <v>65</v>
@@ -8110,7 +8120,7 @@
         </is>
       </c>
       <c r="G11" s="13" t="n">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="H11" s="35" t="n">
         <v>36</v>
@@ -8147,7 +8157,7 @@
         </is>
       </c>
       <c r="G12" s="17" t="n">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="H12" s="28" t="n">
         <v>18</v>
@@ -8184,7 +8194,7 @@
         </is>
       </c>
       <c r="G13" s="13" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="H13" s="35" t="n">
         <v>32</v>
@@ -8221,7 +8231,7 @@
         </is>
       </c>
       <c r="G14" s="17" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="H14" s="28" t="n">
         <v>18</v>
@@ -8262,7 +8272,7 @@
         </is>
       </c>
       <c r="G15" s="13" t="n">
-        <v>46561</v>
+        <v>46562</v>
       </c>
       <c r="H15" s="35" t="n">
         <v>45</v>
@@ -8299,7 +8309,7 @@
         </is>
       </c>
       <c r="G16" s="17" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H16" s="28" t="n">
         <v>35</v>
@@ -8340,7 +8350,7 @@
         </is>
       </c>
       <c r="G17" s="13" t="n">
-        <v>46501</v>
+        <v>46502</v>
       </c>
       <c r="H17" s="35" t="n">
         <v>38</v>
@@ -8377,7 +8387,7 @@
         </is>
       </c>
       <c r="G18" s="17" t="n">
-        <v>46566</v>
+        <v>46567</v>
       </c>
       <c r="H18" s="28" t="n">
         <v>22</v>
@@ -8418,7 +8428,7 @@
         </is>
       </c>
       <c r="G19" s="13" t="n">
-        <v>46381</v>
+        <v>46382</v>
       </c>
       <c r="H19" s="35" t="n">
         <v>22</v>
@@ -8720,10 +8730,10 @@
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
@@ -8764,10 +8774,10 @@
         </is>
       </c>
       <c r="B6" s="17" t="n">
-        <v>46235</v>
+        <v>46236</v>
       </c>
       <c r="C6" s="17" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
@@ -8808,10 +8818,10 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
@@ -8852,10 +8862,10 @@
         </is>
       </c>
       <c r="B8" s="17" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
@@ -9077,7 +9087,7 @@
     </row>
     <row r="5">
       <c r="A5" s="13" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
@@ -9115,7 +9125,7 @@
     </row>
     <row r="6">
       <c r="A6" s="17" t="n">
-        <v>46206</v>
+        <v>46207</v>
       </c>
       <c r="B6" s="18" t="inlineStr">
         <is>
@@ -9153,7 +9163,7 @@
     </row>
     <row r="7">
       <c r="A7" s="13" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
@@ -9191,7 +9201,7 @@
     </row>
     <row r="8">
       <c r="A8" s="17" t="n">
-        <v>46213</v>
+        <v>46214</v>
       </c>
       <c r="B8" s="18" t="inlineStr">
         <is>
@@ -9229,7 +9239,7 @@
     </row>
     <row r="9">
       <c r="A9" s="13" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
@@ -9267,7 +9277,7 @@
     </row>
     <row r="10">
       <c r="A10" s="17" t="n">
-        <v>46221</v>
+        <v>46222</v>
       </c>
       <c r="B10" s="18" t="inlineStr">
         <is>
@@ -9305,7 +9315,7 @@
     </row>
     <row r="11">
       <c r="A11" s="13" t="n">
-        <v>46228</v>
+        <v>46229</v>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
